--- a/data/trans_orig/IQ17B_M_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ17B_M_R-Clase-trans_orig.xlsx
@@ -716,17 +716,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,11; 9,56</t>
+          <t>5,14; 9,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,45; 6,53</t>
+          <t>4,43; 6,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,39; 6,65</t>
+          <t>4,34; 6,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -736,42 +736,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,82; 7,32</t>
+          <t>4,72; 7,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,42; 8,52</t>
+          <t>5,29; 8,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,27; 8,59</t>
+          <t>4,23; 8,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,78; 18,4</t>
+          <t>6,73; 18,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,28; 7,88</t>
+          <t>5,22; 7,71</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,19; 7,02</t>
+          <t>5,15; 7,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,62; 7,04</t>
+          <t>4,6; 6,8</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,35; 14,14</t>
+          <t>7,26; 13,79</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,73; 7,26</t>
+          <t>4,73; 7,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,0; 5,78</t>
+          <t>4,1; 5,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,44; 6,13</t>
+          <t>4,47; 6,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,04; 8,41</t>
+          <t>6,03; 8,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,76; 10,05</t>
+          <t>4,69; 9,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,1; 7,69</t>
+          <t>5,08; 7,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,25; 7,38</t>
+          <t>5,26; 7,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,91; 12,55</t>
+          <t>7,81; 12,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,95; 7,23</t>
+          <t>4,99; 7,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,89; 6,57</t>
+          <t>4,87; 6,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,09; 6,54</t>
+          <t>5,09; 6,49</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,22; 9,74</t>
+          <t>7,24; 9,56</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,8; 7,34</t>
+          <t>4,82; 7,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,84; 7,47</t>
+          <t>4,89; 7,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,4; 7,18</t>
+          <t>4,27; 7,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,59; 14,1</t>
+          <t>7,66; 14,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,2; 8,03</t>
+          <t>5,24; 7,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,76; 13,91</t>
+          <t>4,8; 12,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,93; 7,47</t>
+          <t>4,99; 7,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,08; 13,05</t>
+          <t>7,88; 13,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,28; 7,28</t>
+          <t>5,26; 7,28</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,2; 9,37</t>
+          <t>5,15; 8,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,0; 6,86</t>
+          <t>4,97; 6,79</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,47; 12,36</t>
+          <t>8,5; 12,59</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,41; 7,36</t>
+          <t>5,42; 7,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,25; 5,78</t>
+          <t>4,2; 5,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,22; 6,96</t>
+          <t>5,2; 6,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,03; 8,05</t>
+          <t>6,08; 8,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,13; 6,94</t>
+          <t>5,06; 6,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,53; 6,53</t>
+          <t>4,57; 6,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,64; 7,52</t>
+          <t>5,67; 7,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,89; 9,64</t>
+          <t>6,79; 9,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,47; 6,72</t>
+          <t>5,44; 6,69</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,62; 5,86</t>
+          <t>4,6; 5,93</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,67; 7,06</t>
+          <t>5,69; 6,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,75; 8,46</t>
+          <t>6,71; 8,47</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,12; 9,53</t>
+          <t>5,22; 9,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,56; 7,91</t>
+          <t>4,55; 7,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,58; 9,02</t>
+          <t>5,57; 9,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,79; 13,22</t>
+          <t>7,73; 13,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,13; 9,07</t>
+          <t>6,19; 9,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,02; 6,73</t>
+          <t>4,92; 6,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,14; 7,58</t>
+          <t>5,14; 7,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,96; 13,93</t>
+          <t>7,92; 13,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,2; 8,75</t>
+          <t>6,14; 8,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,99; 6,75</t>
+          <t>5,02; 6,9</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,69; 7,67</t>
+          <t>5,65; 7,61</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,16; 12,37</t>
+          <t>8,18; 12,35</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,25; 7,67</t>
+          <t>5,26; 7,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,2; 6,89</t>
+          <t>4,2; 7,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,84; 7,89</t>
+          <t>4,87; 7,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,98; 11,37</t>
+          <t>7,91; 11,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,84; 7,66</t>
+          <t>4,86; 7,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,04; 8,34</t>
+          <t>4,98; 8,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,4; 11,26</t>
+          <t>6,55; 11,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,88; 11,03</t>
+          <t>7,66; 10,66</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,38; 7,22</t>
+          <t>5,36; 7,17</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,96; 7,13</t>
+          <t>5,0; 7,22</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,1; 8,87</t>
+          <t>6,01; 9,0</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,34; 10,54</t>
+          <t>8,38; 10,63</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,73; 6,97</t>
+          <t>5,73; 6,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,87; 5,83</t>
+          <t>4,87; 5,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,52; 6,59</t>
+          <t>5,48; 6,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,52; 9,05</t>
+          <t>7,55; 8,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,78; 6,81</t>
+          <t>5,7; 6,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,52; 6,66</t>
+          <t>5,49; 6,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,89; 6,99</t>
+          <t>5,83; 6,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,33; 10,8</t>
+          <t>8,39; 10,83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,85; 6,62</t>
+          <t>5,88; 6,7</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,31; 6,07</t>
+          <t>5,27; 6,03</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,85; 6,58</t>
+          <t>5,84; 6,56</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,18; 9,67</t>
+          <t>8,16; 9,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ17B_M_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ17B_M_R-Clase-trans_orig.xlsx
@@ -526,13 +526,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores en función del número de meses de su última consulta al médico (tasa de respuesta: 91,3%)</t>
+          <t>Tiempo medio en meses desde la última consulta médica por algo que le pasaba a su hijo/a (tasa de respuesta: 91,3%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,81</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6,55</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5,6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9,28</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>6,43</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>5,39</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>5,41</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8,27</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,81</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,55</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,6</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,6</t>
+          <t>8,47</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,04</t>
+          <t>8,91</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,14; 9,25</t>
+          <t>4,82; 7,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,43; 6,57</t>
+          <t>5,31; 8,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,34; 6,52</t>
+          <t>4,29; 8,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,95; 10,11</t>
+          <t>7,19; 15,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,72; 7,14</t>
+          <t>5,06; 9,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,29; 8,33</t>
+          <t>4,49; 6,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,23; 8,68</t>
+          <t>4,39; 6,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,73; 18,33</t>
+          <t>7,03; 10,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,22; 7,71</t>
+          <t>5,13; 7,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,15; 7,01</t>
+          <t>5,21; 7,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,6; 6,8</t>
+          <t>4,69; 7,02</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,26; 13,79</t>
+          <t>7,62; 12,11</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5,92</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6,23</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6,22</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9,76</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>5,71</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>4,83</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>5,27</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7,06</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,92</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,23</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>6,22</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,66</t>
+          <t>7,2</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,27</t>
+          <t>8,35</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,73; 7,21</t>
+          <t>4,7; 8,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,1; 5,84</t>
+          <t>5,05; 7,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,47; 6,32</t>
+          <t>5,08; 7,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,03; 8,31</t>
+          <t>7,94; 12,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,69; 9,57</t>
+          <t>4,68; 7,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,08; 7,66</t>
+          <t>4,06; 5,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,26; 7,44</t>
+          <t>4,48; 6,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,81; 12,37</t>
+          <t>6,12; 8,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,99; 7,4</t>
+          <t>4,99; 7,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,87; 6,49</t>
+          <t>4,86; 6,52</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,09; 6,49</t>
+          <t>5,06; 6,57</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,24; 9,56</t>
+          <t>7,31; 9,58</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6,39</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6,56</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6,02</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10,82</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5,83</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5,92</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>5,48</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9,56</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,39</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,56</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,02</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,54</t>
+          <t>9,69</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,06</t>
+          <t>10,23</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,82; 7,51</t>
+          <t>5,25; 8,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,89; 7,5</t>
+          <t>4,76; 12,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,27; 7,06</t>
+          <t>4,95; 7,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,66; 14,18</t>
+          <t>8,62; 13,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,24; 7,97</t>
+          <t>4,91; 7,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,8; 12,08</t>
+          <t>4,84; 7,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 7,48</t>
+          <t>4,34; 7,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,88; 13,11</t>
+          <t>7,74; 14,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,26; 7,28</t>
+          <t>5,32; 7,14</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,15; 8,77</t>
+          <t>5,13; 8,98</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,97; 6,79</t>
+          <t>4,98; 6,76</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,5; 12,59</t>
+          <t>8,78; 12,47</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5,84</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5,36</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,56</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8,33</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>6,21</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>4,88</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>6,01</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,02</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,84</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,36</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,56</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,02</t>
+          <t>7,32</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,52</t>
+          <t>7,83</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,42; 7,37</t>
+          <t>5,08; 6,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,2; 5,76</t>
+          <t>4,58; 6,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,2; 6,98</t>
+          <t>5,69; 7,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,08; 8,09</t>
+          <t>7,0; 9,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,06; 6,7</t>
+          <t>5,46; 7,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 6,71</t>
+          <t>4,19; 5,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,67; 7,62</t>
+          <t>5,26; 6,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,79; 9,7</t>
+          <t>6,47; 8,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,44; 6,69</t>
+          <t>5,48; 6,68</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 5,93</t>
+          <t>4,61; 5,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,69; 6,96</t>
+          <t>5,65; 6,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,71; 8,47</t>
+          <t>7,01; 8,99</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7,4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5,79</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6,11</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10,0</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>6,71</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>5,48</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>6,97</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9,4</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,4</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,79</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,11</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,92</t>
+          <t>9,69</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,7</t>
+          <t>9,86</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,22; 9,68</t>
+          <t>6,28; 9,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,55; 7,81</t>
+          <t>5,0; 6,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,57; 9,17</t>
+          <t>5,1; 7,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,73; 13,93</t>
+          <t>8,05; 13,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,19; 9,02</t>
+          <t>5,22; 9,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,92; 6,69</t>
+          <t>4,6; 8,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,14; 7,76</t>
+          <t>5,71; 9,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,92; 13,7</t>
+          <t>7,98; 13,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,14; 8,63</t>
+          <t>6,07; 8,52</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,02; 6,9</t>
+          <t>5,06; 6,93</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,65; 7,61</t>
+          <t>5,72; 7,86</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,18; 12,35</t>
+          <t>8,46; 12,21</t>
         </is>
       </c>
     </row>
@@ -1348,42 +1348,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5,88</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6,36</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8,17</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9,48</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>6,39</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>5,35</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>6,15</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9,54</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5,88</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>6,36</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>8,17</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9,22</t>
+          <t>9,78</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,37</t>
+          <t>9,62</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,26; 7,62</t>
+          <t>4,8; 7,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,2; 7,16</t>
+          <t>4,88; 8,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,87; 7,86</t>
+          <t>6,5; 11,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,91; 11,17</t>
+          <t>8,07; 11,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,86; 7,68</t>
+          <t>5,36; 7,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,98; 8,27</t>
+          <t>4,25; 6,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,55; 11,37</t>
+          <t>4,81; 7,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,66; 10,66</t>
+          <t>8,11; 11,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,36; 7,17</t>
+          <t>5,44; 7,04</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,0; 7,22</t>
+          <t>4,88; 7,15</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,01; 9,0</t>
+          <t>6,11; 8,83</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,38; 10,63</t>
+          <t>8,37; 10,73</t>
         </is>
       </c>
     </row>
@@ -1488,42 +1488,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6,22</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5,97</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6,39</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>9,4</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>6,24</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>5,24</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>5,97</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8,16</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6,22</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,97</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,39</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>9,29</t>
+          <t>8,43</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,75</t>
+          <t>8,92</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,73; 6,98</t>
+          <t>5,73; 6,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,87; 5,81</t>
+          <t>5,47; 6,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,48; 6,55</t>
+          <t>5,89; 6,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,55; 8,93</t>
+          <t>8,51; 10,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,7; 6,82</t>
+          <t>5,72; 6,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,49; 6,7</t>
+          <t>4,85; 5,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,83; 6,98</t>
+          <t>5,44; 6,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,39; 10,83</t>
+          <t>7,87; 9,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,88; 6,7</t>
+          <t>5,85; 6,67</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,27; 6,03</t>
+          <t>5,29; 6,03</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,84; 6,56</t>
+          <t>5,8; 6,59</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,16; 9,66</t>
+          <t>8,35; 9,68</t>
         </is>
       </c>
     </row>
